--- a/test_doc/new_org/syllabus_7_science.xlsx
+++ b/test_doc/new_org/syllabus_7_science.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,16 +441,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
+          <t>Respiration in Organisms</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Photosynthesis</t>
+          <t>Why we breathe</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -461,22 +461,22 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other modes of nutrition</t>
+          <t>Breathing in animals</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nutrition in Animals</t>
+          <t>Changes Around Us</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Digestion in humans</t>
+          <t>Reversible changes</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -491,26 +491,26 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Digestion in grass-eaters</t>
+          <t>Irreversible changes</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Winds, Storms and Cyclones</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hot and cold</t>
+          <t>Air pressure</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -521,26 +521,26 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Transfer of heat</t>
+          <t>Staying safe in storms</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Acids, Bases and Salts</t>
+          <t>Electricity and Circuits</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>Cells and bulbs</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -551,26 +551,26 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Neutralisation</t>
+          <t>Conductors and insulators</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Physical and Chemical Changes</t>
+          <t>Living Organisms</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kinds of changes</t>
+          <t>Habitats</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -581,22 +581,22 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rusting and crystallisation</t>
+          <t>Adaptation</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Weather, Climate and Adaptations</t>
+          <t>Separation of Substances</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Weather vs climate</t>
+          <t>Sieving and winnowing</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -611,26 +611,26 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Animals in extreme climates</t>
+          <t>Filtration and evaporation</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Winds, Storms and Cyclones</t>
+          <t>Fibre to Fabric</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Air pressure</t>
+          <t>Plant fibres</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -641,26 +641,26 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Staying safe in storms</t>
+          <t>Spinning and weaving</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Soil</t>
+          <t>Nutrition in Animals</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Soil profile</t>
+          <t>Digestion in humans</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Soil and crops</t>
+          <t>Digestion in grass-eaters</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -681,16 +681,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Respiration in Organisms</t>
+          <t>Nutrition in Plants</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Why we breathe</t>
+          <t>Photosynthesis</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -701,26 +701,26 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Breathing in animals</t>
+          <t>Other modes of nutrition</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Electric Current and Its Effects</t>
+          <t>Physical and Chemical Changes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Heating effect</t>
+          <t>Kinds of changes</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Magnetic effect</t>
+          <t>Rusting and crystallisation</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -741,12 +741,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Body Movements</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Reflection</t>
+          <t>Joints</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -761,10 +761,20 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Images and mirrors</t>
+          <t>Skeleton</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Animal movement</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>4</v>
       </c>
     </row>
